--- a/public/actius.xlsx
+++ b/public/actius.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733A4C10-7412-422E-91FB-DEC856CC7876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B455CE35-01A3-4145-8310-03E5858EFC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
   <si>
     <t>Bitcoin</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Rendiment (%)</t>
   </si>
   <si>
-    <t>Variació 🪙/$ (%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">🪙/$ </t>
   </si>
   <si>
@@ -179,6 +176,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Variació moneda local / dòlar EUA (%)</t>
   </si>
 </sst>
 </file>
@@ -881,10 +881,10 @@
         <v>17</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="21">
         <v>2025</v>
@@ -908,7 +908,7 @@
         <v>27</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>14</v>
@@ -929,14 +929,13 @@
       </c>
       <c r="B2" s="24">
         <f>(100*(H2/100+1))*(G2/100+1)*(F2/100+1)*(E2/100+1)*(D2/100+1)</f>
-        <v>314.82111281390223</v>
-      </c>
-      <c r="C2" s="25">
-        <f>(1-(((100*(H2/100+1))*(G2/100+1)*(F2/100+1)*(E2/100+1)*(D2/100+1))/B2))*100</f>
-        <v>0</v>
+        <v>320.14507041045545</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D2" s="10">
-        <v>-6.57</v>
+        <v>-4.99</v>
       </c>
       <c r="E2" s="10">
         <v>126.6</v>
@@ -954,10 +953,10 @@
         <v>7</v>
       </c>
       <c r="K2" s="3">
-        <v>53.08829101932551</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
+        <v>65.900000000000006</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M2" s="27"/>
       <c r="N2" s="16" t="s">
@@ -980,14 +979,13 @@
       </c>
       <c r="B3" s="24">
         <f>(100*(H3/100+1))*(G3/100+1)*(F3/100+1)*(E3/100+1)*(D3/100+1)</f>
-        <v>213.37424664827586</v>
-      </c>
-      <c r="C3" s="25">
-        <f>(1-(((100*(H3/100+1))*(G3/100+1)*(F3/100+1)*(E3/100+1)*(D3/100+1))/B3))*100</f>
-        <v>0</v>
+        <v>231.23118876857998</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D3" s="10">
-        <v>53.08829101932551</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="E3" s="10">
         <v>30</v>
@@ -1005,10 +1003,10 @@
         <v>25</v>
       </c>
       <c r="K3" s="3">
-        <v>41.596638655462186</v>
+        <v>52.93</v>
       </c>
       <c r="L3" s="3">
-        <v>7.9</v>
+        <v>13.96</v>
       </c>
       <c r="M3" s="27"/>
       <c r="N3" s="16" t="s">
@@ -1031,14 +1029,13 @@
       </c>
       <c r="B4" s="24">
         <f>(100*(H4/100+1))*(G4/100+1)*(F4/100+1)*(E4/100+1)*(D4/100+1)</f>
-        <v>174.5308660339405</v>
-      </c>
-      <c r="C4" s="25">
-        <f t="shared" ref="C4:C21" si="1">(1-(((100*(H4/100+1))*(G4/100+1)*(F4/100+1)*(E4/100+1)*(D4/100+1))/B4))*100</f>
-        <v>0</v>
+        <v>183.96220024112989</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D4" s="10">
-        <v>11.409624213569117</v>
+        <v>17.43</v>
       </c>
       <c r="E4" s="10">
         <v>24.1</v>
@@ -1052,14 +1049,14 @@
       <c r="H4" s="10">
         <v>26.9</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>2</v>
+      <c r="J4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K4" s="3">
-        <v>31.063363078917206</v>
+        <v>34.46</v>
       </c>
       <c r="L4" s="3">
-        <v>2.5099999999999998</v>
+        <v>14.61</v>
       </c>
       <c r="M4" s="27"/>
       <c r="N4" s="17" t="s">
@@ -1077,40 +1074,39 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="11" t="s">
-        <v>10</v>
+      <c r="A5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B5" s="24">
         <f>(100*(H5/100+1))*(G5/100+1)*(F5/100+1)*(E5/100+1)*(D5/100+1)</f>
-        <v>161.82927713077004</v>
-      </c>
-      <c r="C5" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>165.88090098230981</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D5" s="10">
-        <v>-1.4625228519195588</v>
+        <v>20.46</v>
       </c>
       <c r="E5" s="10">
-        <v>2.2000000000000002</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="F5" s="10">
-        <v>-4.8</v>
+        <v>20.9</v>
       </c>
       <c r="G5" s="10">
-        <v>19.8</v>
+        <v>-19.899999999999999</v>
       </c>
       <c r="H5" s="10">
-        <v>40.9</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>9</v>
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K5" s="3">
-        <v>26.976744186046517</v>
+        <v>32.44</v>
       </c>
       <c r="L5" s="3">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="M5" s="27"/>
       <c r="N5" s="7" t="s">
@@ -1128,40 +1124,39 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
+      <c r="A6" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="24">
         <f>(100*(H6/100+1))*(G6/100+1)*(F6/100+1)*(E6/100+1)*(D6/100+1)</f>
-        <v>157.39819842502084</v>
-      </c>
-      <c r="C6" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>164.72388948850238</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D6" s="10">
-        <v>14.3</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="10">
-        <v>18.399999999999999</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F6" s="10">
-        <v>20.9</v>
+        <v>-4.8</v>
       </c>
       <c r="G6" s="10">
-        <v>-19.899999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="H6" s="10">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>40.9</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="K6" s="3">
-        <v>24.225774225774231</v>
-      </c>
-      <c r="L6" s="3">
-        <v>10.85</v>
+        <v>30.53</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M6" s="27"/>
       <c r="N6" s="2" t="s">
@@ -1179,40 +1174,40 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6" t="s">
-        <v>19</v>
+      <c r="A7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="24">
-        <f>((7300*(H7/100+1))*(G7/100+1)*(F7/100+1)*(E7/100+1)*(D7/100+1))/88</f>
-        <v>153.55867389988978</v>
+        <f>((1440*(H7/100+1))*(G7/100+1)*(F7/100+1)*(E7/100+1)*(D7/100+1))/16.58</f>
+        <v>163.06689577253454</v>
       </c>
       <c r="C7" s="25">
-        <f>(1-(((100*(H7/100+1))*(G7/100+1)*(F7/100+1)*(E7/100+1)*(D7/100+1))/B7))*100</f>
-        <v>-20.547945205479444</v>
+        <f t="shared" ref="C7:C13" si="1">(1-(((100*(H7/100+1))*(G7/100+1)*(F7/100+1)*(E7/100+1)*(D7/100+1))/B7))*100</f>
+        <v>-15.138888888888879</v>
       </c>
       <c r="D7" s="10">
-        <v>7.5</v>
+        <v>52.93</v>
       </c>
       <c r="E7" s="10">
-        <v>8.1999999999999993</v>
+        <v>7.0694087403599042</v>
       </c>
       <c r="F7" s="10">
-        <v>23</v>
+        <v>5.7783820530251546</v>
       </c>
       <c r="G7" s="10">
-        <v>1.8</v>
+        <v>-1.0759919300605247</v>
       </c>
       <c r="H7" s="10">
-        <v>27.1</v>
+        <v>9.579955784819461</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" s="3">
-        <v>20.539429488143583</v>
+        <v>28.89</v>
       </c>
       <c r="L7" s="3">
-        <v>3.8</v>
+        <v>4.18</v>
       </c>
       <c r="M7" s="27"/>
       <c r="N7" s="2" t="s">
@@ -1234,15 +1229,15 @@
         <v>4</v>
       </c>
       <c r="B8" s="24">
-        <f>((82*(H8/100+1))*(G8/100+1)*(F8/100+1)*(E8/100+1)*(D8/100+1))/0.86</f>
-        <v>148.36189046959282</v>
+        <f>((82*(H8/100+1))*(G8/100+1)*(F8/100+1)*(E8/100+1)*(D8/100+1))/0.85</f>
+        <v>157.29802750702083</v>
       </c>
       <c r="C8" s="25">
-        <f>(1-(((100*(H8/100+1))*(G8/100+1)*(F8/100+1)*(E8/100+1)*(D8/100+1))/B8))*100</f>
-        <v>-4.8780487804878092</v>
+        <f t="shared" si="1"/>
+        <v>-3.6585365853658791</v>
       </c>
       <c r="D8" s="10">
-        <v>12.911133810010213</v>
+        <v>18.32</v>
       </c>
       <c r="E8" s="10">
         <v>8</v>
@@ -1256,14 +1251,14 @@
       <c r="H8" s="10">
         <v>21.2</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>20</v>
+      <c r="J8" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
-        <v>18.684248268414706</v>
+        <v>26.18</v>
       </c>
       <c r="L8" s="3">
-        <v>13.12</v>
+        <v>0.94</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="2" t="s">
@@ -1281,40 +1276,40 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
+      <c r="A9" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B9" s="24">
-        <f>((1440*(H9/100+1))*(G9/100+1)*(F9/100+1)*(E9/100+1)*(D9/100+1))/17.36</f>
-        <v>144.19854042360996</v>
+        <f>((7300*(H9/100+1))*(G9/100+1)*(F9/100+1)*(E9/100+1)*(D9/100+1))/89.79</f>
+        <v>153.57736676119998</v>
       </c>
       <c r="C9" s="25">
-        <f>(1-(((100*(H9/100+1))*(G9/100+1)*(F9/100+1)*(E9/100+1)*(D9/100+1))/B9))*100</f>
-        <v>-20.555555555555571</v>
+        <f t="shared" si="1"/>
+        <v>-23.000000000000021</v>
       </c>
       <c r="D9" s="10">
-        <v>41.596638655462186</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="E9" s="10">
-        <v>7.0694087403599042</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="F9" s="10">
-        <v>5.7783820530251546</v>
+        <v>23</v>
       </c>
       <c r="G9" s="10">
-        <v>-1.0759919300605247</v>
+        <v>1.8</v>
       </c>
       <c r="H9" s="10">
-        <v>9.579955784819461</v>
+        <v>27.1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K9" s="3">
-        <v>18.660977732492725</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
+        <v>20.46</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M9" s="27"/>
       <c r="N9" s="2" t="s">
@@ -1336,15 +1331,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="24">
-        <f>((82*(H10/100+1))*(G10/100+1)*(F10/100+1)*(E10/100+1)*(D10/100+1))/0.86</f>
-        <v>136.60133300815465</v>
+        <f>((82*(H10/100+1))*(G10/100+1)*(F10/100+1)*(E10/100+1)*(D10/100+1))/0.85</f>
+        <v>144.65264220060834</v>
       </c>
       <c r="C10" s="25">
-        <f>(1-(((100*(H10/100+1))*(G10/100+1)*(F10/100+1)*(E10/100+1)*(D10/100+1))/B10))*100</f>
-        <v>-4.878048780487787</v>
+        <f t="shared" si="1"/>
+        <v>-3.6585365853658569</v>
       </c>
       <c r="D10" s="10">
-        <v>10.832232496697486</v>
+        <v>16</v>
       </c>
       <c r="E10" s="10">
         <v>11.2</v>
@@ -1359,13 +1354,13 @@
         <v>3.1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K10" s="3">
-        <v>14.29727542487187</v>
+        <v>18.32</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="M10" s="27"/>
       <c r="N10" s="6" t="s">
@@ -1383,40 +1378,40 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
+      <c r="A11" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="B11" s="24">
-        <f>((374*(H11/100+1))*(G11/100+1)*(F11/100+1)*(E11/100+1)*(D11/100+1))/3.73</f>
-        <v>133.02918824053214</v>
+        <f>((519*(H11/100+1))*(G11/100+1)*(F11/100+1)*(E11/100+1)*(D11/100+1))/5.49</f>
+        <v>139.44759238675249</v>
       </c>
       <c r="C11" s="25">
         <f t="shared" si="1"/>
-        <v>0.26737967914435279</v>
+        <v>-5.7803468208092568</v>
       </c>
       <c r="D11" s="10">
-        <v>-4.2206713193752137</v>
+        <v>34.46</v>
       </c>
       <c r="E11" s="10">
-        <v>0.57658561042867973</v>
+        <v>-1.2</v>
       </c>
       <c r="F11" s="10">
-        <v>14.210727238022528</v>
+        <v>12.6</v>
       </c>
       <c r="G11" s="10">
-        <v>-7.1181632833968678</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="H11" s="10">
-        <v>29.830820577741974</v>
+        <v>-2.5</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3">
-        <v>12.911133810010213</v>
-      </c>
-      <c r="L11" s="3">
-        <v>10.85</v>
+        <v>17.43</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M11" s="27"/>
     </row>
@@ -1425,15 +1420,15 @@
         <v>24</v>
       </c>
       <c r="B12" s="24">
-        <f>((82*(H12/100+1))*(G12/100+1)*(F12/100+1)*(E12/100+1)*(D12/100+1))/0.86</f>
-        <v>128.87639029322548</v>
+        <f>((82*(H12/100+1))*(G12/100+1)*(F12/100+1)*(E12/100+1)*(D12/100+1))/0.85</f>
+        <v>139.014579028133</v>
       </c>
       <c r="C12" s="25">
-        <f>(1-(((100*(H12/100+1))*(G12/100+1)*(F12/100+1)*(E12/100+1)*(D12/100+1))/B12))*100</f>
-        <v>-4.8780487804878314</v>
+        <f t="shared" si="1"/>
+        <v>-3.6585365853658569</v>
       </c>
       <c r="D12" s="10">
-        <v>24.225774225774231</v>
+        <v>32.44</v>
       </c>
       <c r="E12" s="10">
         <v>-0.8910891089108901</v>
@@ -1448,51 +1443,51 @@
         <v>13.75</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" s="3">
-        <v>11.409624213569117</v>
+        <v>16</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>13.63</v>
       </c>
       <c r="M12" s="27"/>
     </row>
     <row r="13" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="23" t="s">
-        <v>20</v>
+      <c r="A13" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="B13" s="24">
-        <f>((519*(H13/100+1))*(G13/100+1)*(F13/100+1)*(E13/100+1)*(D13/100+1))/5.52</f>
-        <v>122.4339607457316</v>
+        <f>((10400*(H13/100+1))*(G13/100+1)*(F13/100+1)*(E13/100+1)*(D13/100+1))/156.31</f>
+        <v>121.98661947998247</v>
       </c>
       <c r="C13" s="25">
         <f t="shared" si="1"/>
-        <v>-6.3583815028901425</v>
+        <v>-50.298076923076927</v>
       </c>
       <c r="D13" s="10">
-        <v>18.7</v>
+        <v>26.18</v>
       </c>
       <c r="E13" s="10">
-        <v>-1.2</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="F13" s="10">
-        <v>12.6</v>
+        <v>27.3</v>
       </c>
       <c r="G13" s="10">
-        <v>1.1399999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="H13" s="10">
-        <v>-2.5</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>6</v>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="K13" s="3">
-        <v>10.832232496697486</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="L13" s="3">
-        <v>10.85</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="M13" s="27"/>
       <c r="O13" s="18"/>
@@ -1500,40 +1495,39 @@
       <c r="Q13" s="20"/>
     </row>
     <row r="14" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="11" t="s">
-        <v>1</v>
+      <c r="A14" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B14" s="24">
-        <f>(100*(H14/100+1))*(G14/100+1)*(F14/100+1)*(E14/100+1)*(D14/100+1)</f>
-        <v>121.70364566126349</v>
-      </c>
-      <c r="C14" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>((374*(H14/100+1))*(G14/100+1)*(F14/100+1)*(E14/100+1)*(D14/100+1))/3.73</f>
+        <v>119.79377642126788</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D14" s="10">
-        <v>-14.86486486486487</v>
+        <v>-13.75</v>
       </c>
       <c r="E14" s="10">
-        <v>-5.0999999999999996</v>
+        <v>0.57658561042867973</v>
       </c>
       <c r="F14" s="10">
-        <v>-9.3000000000000007</v>
+        <v>14.210727238022528</v>
       </c>
       <c r="G14" s="10">
-        <v>10.5</v>
+        <v>-7.1181632833968678</v>
       </c>
       <c r="H14" s="10">
-        <v>50.3</v>
+        <v>29.830820577741974</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="3">
-        <v>9.7928667728888286</v>
+        <v>6.84</v>
       </c>
       <c r="L14" s="3">
-        <v>4.5999999999999996</v>
+        <v>8.17</v>
       </c>
       <c r="M14" s="27"/>
       <c r="O14" s="18"/>
@@ -1542,153 +1536,150 @@
     </row>
     <row r="15" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" s="24">
-        <f>((10400*(H15/100+1))*(G15/100+1)*(F15/100+1)*(E15/100+1)*(D15/100+1))/151</f>
-        <v>120.63147012361414</v>
-      </c>
-      <c r="C15" s="25">
-        <f>(1-(((100*(H15/100+1))*(G15/100+1)*(F15/100+1)*(E15/100+1)*(D15/100+1))/B15))*100</f>
-        <v>-45.192307692307708</v>
+        <f>(100*(H15/100+1))*(G15/100+1)*(F15/100+1)*(E15/100+1)*(D15/100+1)</f>
+        <v>117.73649317348618</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D15" s="10">
-        <v>20.539429488143583</v>
+        <v>-17.64</v>
       </c>
       <c r="E15" s="10">
-        <v>20.100000000000001</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="F15" s="10">
-        <v>27.3</v>
+        <v>-9.3000000000000007</v>
       </c>
       <c r="G15" s="10">
-        <v>-9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H15" s="10">
-        <v>4.9000000000000004</v>
+        <v>50.3</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K15" s="3">
-        <v>7.559128807214563</v>
-      </c>
-      <c r="L15" s="3">
-        <v>-3.47</v>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M15" s="27"/>
     </row>
     <row r="16" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="24">
+        <f>((131*(H16/100+1))*(G16/100+1)*(F16/100+1)*(E16/100+1)*(D16/100+1))/1.49</f>
+        <v>116.35047919279687</v>
+      </c>
+      <c r="C16" s="25">
+        <f>(1-(((100*(H16/100+1))*(G16/100+1)*(F16/100+1)*(E16/100+1)*(D16/100+1))/B16))*100</f>
+        <v>-13.740458015267176</v>
+      </c>
+      <c r="D16" s="10">
+        <v>6.84</v>
+      </c>
+      <c r="E16" s="10">
+        <v>7.49670619235836</v>
+      </c>
+      <c r="F16" s="10">
+        <v>7.8431372549019613</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-5.4540569586243919</v>
+      </c>
+      <c r="H16" s="10">
+        <v>13.010475178381654</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="L16" s="3">
+        <v>13.63</v>
+      </c>
+      <c r="M16" s="27"/>
+    </row>
+    <row r="17" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="24">
+        <f>(100*(H17/100+1))*(G17/100+1)*(F17/100+1)*(E17/100+1)*(D17/100+1)</f>
+        <v>115.53934697342996</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E17" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="F17" s="10">
+        <v>3.5</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="27"/>
+    </row>
+    <row r="18" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B16" s="24">
-        <f>(100*(H16/100+1))*(G16/100+1)*(F16/100+1)*(E16/100+1)*(D16/100+1)</f>
-        <v>118.72763634517385</v>
-      </c>
-      <c r="C16" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D16" s="10">
-        <v>1.0731690948277048</v>
-      </c>
-      <c r="E16" s="10">
-        <v>7.0044505144289246</v>
-      </c>
-      <c r="F16" s="10">
-        <v>-10.540658075248288</v>
-      </c>
-      <c r="G16" s="10">
-        <v>-0.4658318185169037</v>
-      </c>
-      <c r="H16" s="10">
-        <v>23.286694095423371</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="3">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="27"/>
-    </row>
-    <row r="17" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="24">
-        <f>((131*(H17/100+1))*(G17/100+1)*(F17/100+1)*(E17/100+1)*(D17/100+1))/1.53</f>
-        <v>116.44028493437756</v>
-      </c>
-      <c r="C17" s="25">
-        <f t="shared" si="1"/>
-        <v>-16.793893129770975</v>
-      </c>
-      <c r="D17" s="10">
-        <v>9.7928667728888286</v>
-      </c>
-      <c r="E17" s="10">
-        <v>7.49670619235836</v>
-      </c>
-      <c r="F17" s="10">
-        <v>7.8431372549019613</v>
-      </c>
-      <c r="G17" s="10">
-        <v>-5.4540569586243919</v>
-      </c>
-      <c r="H17" s="10">
-        <v>13.010475178381654</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2.63</v>
-      </c>
-      <c r="L17" s="3">
-        <v>10.85</v>
-      </c>
-      <c r="M17" s="27"/>
-    </row>
-    <row r="18" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="23" t="s">
-        <v>15</v>
       </c>
       <c r="B18" s="24">
         <f>(100*(H18/100+1))*(G18/100+1)*(F18/100+1)*(E18/100+1)*(D18/100+1)</f>
-        <v>115.53934697342996</v>
-      </c>
-      <c r="C18" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>115.08243618861577</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D18" s="10">
-        <v>4.5999999999999996</v>
+        <v>-2.0299999999999998</v>
       </c>
       <c r="E18" s="10">
-        <v>3.9</v>
+        <v>7.0044505144289246</v>
       </c>
       <c r="F18" s="10">
-        <v>3.5</v>
+        <v>-10.540658075248288</v>
       </c>
       <c r="G18" s="10">
-        <v>1.7</v>
+        <v>-0.4658318185169037</v>
       </c>
       <c r="H18" s="10">
-        <v>1</v>
+        <v>23.286694095423371</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K18" s="3">
-        <v>1.0731690948277048</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
+        <v>-2.0299999999999998</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M18" s="27"/>
       <c r="Q18" s="13"/>
@@ -1699,14 +1690,13 @@
       </c>
       <c r="B19" s="24">
         <f>(100*(H19/100+1))*(G19/100+1)*(F19/100+1)*(E19/100+1)*(D19/100+1)</f>
-        <v>105.69084068240373</v>
-      </c>
-      <c r="C19" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>108.64844206479648</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="D19" s="10">
-        <v>26.976744186046517</v>
+        <v>30.53</v>
       </c>
       <c r="E19" s="10">
         <v>7.8</v>
@@ -1721,13 +1711,13 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3">
-        <v>-1.4625228519195588</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
+        <v>-4.99</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="Q19" s="5"/>
     </row>
@@ -1736,15 +1726,15 @@
         <v>18</v>
       </c>
       <c r="B20" s="24">
-        <f>((82*(H20/100+1))*(G20/100+1)*(F20/100+1)*(E20/100+1)*(D20/100+1))/0.86</f>
-        <v>101.5700053925668</v>
+        <f>((82*(H20/100+1))*(G20/100+1)*(F20/100+1)*(E20/100+1)*(D20/100+1))/0.85</f>
+        <v>102.94549997941782</v>
       </c>
       <c r="C20" s="25">
-        <f t="shared" si="1"/>
-        <v>-4.8780487804878092</v>
+        <f>(1-(((100*(H20/100+1))*(G20/100+1)*(F20/100+1)*(E20/100+1)*(D20/100+1))/B20))*100</f>
+        <v>-3.6585365853658569</v>
       </c>
       <c r="D20" s="10">
-        <v>2.4500000000000002</v>
+        <v>2.63</v>
       </c>
       <c r="E20" s="10">
         <v>2.16</v>
@@ -1762,10 +1752,10 @@
         <v>22</v>
       </c>
       <c r="K20" s="3">
-        <v>-4.2206713193752137</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+        <v>-13.75</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="Q20" s="5"/>
     </row>
@@ -1774,15 +1764,15 @@
         <v>2</v>
       </c>
       <c r="B21" s="24">
-        <f>((654*(H21/100+1))*(G21/100+1)*(F21/100+1)*(E21/100+1)*(D21/100+1))/7.11</f>
-        <v>88.704262679284696</v>
+        <f>((654*(H21/100+1))*(G21/100+1)*(F21/100+1)*(E21/100+1)*(D21/100+1))/7</f>
+        <v>88.604130282960824</v>
       </c>
       <c r="C21" s="25">
-        <f t="shared" si="1"/>
-        <v>-8.7155963302752326</v>
+        <f>(1-(((100*(H21/100+1))*(G21/100+1)*(F21/100+1)*(E21/100+1)*(D21/100+1))/B21))*100</f>
+        <v>-7.0336391437309187</v>
       </c>
       <c r="D21" s="10">
-        <v>31.063363078917206</v>
+        <v>28.89</v>
       </c>
       <c r="E21" s="10">
         <v>21.4</v>
@@ -1800,10 +1790,10 @@
         <v>1</v>
       </c>
       <c r="K21" s="3">
-        <v>-14.86486486486487</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
+        <v>-17.64</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="Q21" s="5"/>
     </row>
@@ -1907,7 +1897,7 @@
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="D2:D22">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1919,7 +1909,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E22">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1931,7 +1921,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F22">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1943,7 +1933,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G22">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1956,9 +1958,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="B9 B11:B21" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1980,31 +1979,31 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="H1" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="I1" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>37</v>
       </c>
       <c r="J1" s="15"/>
       <c r="K1" s="15"/>
@@ -2038,7 +2037,7 @@
         <v>1000.3246226261969</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
@@ -2046,7 +2045,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="31">
         <v>1000</v>
@@ -2072,7 +2071,7 @@
         <v>1005.1287707494622</v>
       </c>
       <c r="I3" s="33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
@@ -2080,7 +2079,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="31">
         <v>1000</v>
@@ -2106,7 +2105,7 @@
         <v>1022.6201696512724</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
@@ -2114,7 +2113,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="31">
         <v>1000</v>
@@ -2137,10 +2136,10 @@
       </c>
       <c r="H5" s="32">
         <f ca="1">((E5*G5)+(((TODAY()-C5)*((D5*(F5/100))*E5))/365))*1.1598</f>
-        <v>989.0754968469073</v>
+        <v>989.221693418173</v>
       </c>
       <c r="I5" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
@@ -2148,7 +2147,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="31">
         <v>1000</v>
@@ -2171,10 +2170,10 @@
       </c>
       <c r="H6" s="32">
         <f ca="1">((E6*G6)+(((TODAY()-C6)*((D6*(F6/100))*E6))/365))</f>
-        <v>1014.2363566528792</v>
+        <v>1014.6489593926052</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -2196,11 +2195,11 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="30">
         <f ca="1">(((SUM(H2:H6)*100)/SUM(B2:B6)))-100</f>
-        <v>0.62770833053434671</v>
+        <v>0.63888431675418644</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
